--- a/DATA/3.რეგიონული მშპ.xlsx
+++ b/DATA/3.რეგიონული მშპ.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40FC39D-85EC-4D1B-BB91-D93A926083A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="მონაცემები" sheetId="2" r:id="rId1"/>
@@ -198,7 +197,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -283,12 +282,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="20">
@@ -530,7 +535,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -668,13 +673,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal_Sheet1" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Style 1 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 3 2" xfId="1"/>
+    <cellStyle name="Normal_Sheet1" xfId="4"/>
+    <cellStyle name="Style 1 2" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1010,7 +1018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1141,7 +1149,7 @@
       <c r="P3" s="29">
         <v>42620.844947911872</v>
       </c>
-      <c r="Q3" s="44">
+      <c r="Q3" s="49">
         <v>49374.720708906709</v>
       </c>
     </row>
@@ -1194,7 +1202,7 @@
       <c r="P4" s="29">
         <v>7686.2917862862278</v>
       </c>
-      <c r="Q4" s="44">
+      <c r="Q4" s="49">
         <v>8634.0245268968592</v>
       </c>
     </row>
@@ -1305,7 +1313,7 @@
       <c r="P6" s="29">
         <v>6347.0787577077144</v>
       </c>
-      <c r="Q6" s="44">
+      <c r="Q6" s="49">
         <v>7203.1510226438331</v>
       </c>
     </row>
@@ -1623,7 +1631,7 @@
       <c r="P12" s="29">
         <v>6072.4432212102101</v>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="49">
         <v>6638.0376947554096</v>
       </c>
     </row>
@@ -8054,7 +8062,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U171"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
